--- a/test_case/rapoo_vh520c_test_cases.xlsx
+++ b/test_case/rapoo_vh520c_test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\daihoc\26-KIEM-THU\hw\hw1\23KTPM3-23127296-HW01\test_case\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29F6BE43-F8F6-438D-A230-598E46A0FD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DE81166-D440-4140-B733-CAAAE8781C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -114,9 +114,6 @@
     <t>TC-05</t>
   </si>
   <si>
-    <t>Kiểm tra bánh xe/nút điều chỉnh âm lượng trên tai nghe</t>
-  </si>
-  <si>
     <t>Tai nghe đang phát nhạc/video</t>
   </si>
   <si>
@@ -347,6 +344,9 @@
   </si>
   <si>
     <t>Âm thanh lọt ra ngoài nhỏ, người ngồi cạnh cách 1m không nghe rõ chi tiết</t>
+  </si>
+  <si>
+    <t>Kiểm tra nút điều chỉnh âm lượng trên tai nghe</t>
   </si>
 </sst>
 </file>
@@ -999,7 +999,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="22.35" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1038,7 +1038,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="75.150000000000006" customHeight="1">
@@ -1058,13 +1058,13 @@
         <v>11</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="H3" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="62.4" customHeight="1">
@@ -1075,22 +1075,22 @@
         <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="75.150000000000006" customHeight="1">
@@ -1110,13 +1110,13 @@
         <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G5" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="75.150000000000006" customHeight="1">
@@ -1136,13 +1136,13 @@
         <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="86.4" customHeight="1">
@@ -1150,42 +1150,42 @@
         <v>27</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="75.150000000000006" customHeight="1">
       <c r="A8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>12</v>
@@ -1194,24 +1194,24 @@
         <v>13</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="75.150000000000006" customHeight="1">
       <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>39</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>12</v>
@@ -1220,50 +1220,50 @@
         <v>13</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="75.150000000000006" customHeight="1">
       <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="F10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>13</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="11" spans="1:14" ht="75.150000000000006" customHeight="1">
       <c r="A11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>12</v>
@@ -1272,163 +1272,163 @@
         <v>13</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="83.4" customHeight="1">
       <c r="A12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="C12" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>65</v>
-      </c>
       <c r="G12" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="105.6" customHeight="1">
       <c r="A13" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="E13" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="F13" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="G13" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="41.4">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="41.4">
       <c r="A15" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G15" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="41.4">
       <c r="A16" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="F16" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>93</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="41.4">
       <c r="A17" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>13</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
